--- a/data/SDW.xlsx
+++ b/data/SDW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025-27 PGDM 2nd Year\Ravinder sir\2025-27 TERM 5\Attendance sheet of term-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sritam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9EE3FE-ED52-488B-8729-8A288A81AFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6AE17B-D2BC-4D66-9844-E87531B677F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B08F1D5C-5F29-445A-A91E-715A454E7E2F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B08F1D5C-5F29-445A-A91E-715A454E7E2F}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="137">
   <si>
     <t>Roll No</t>
   </si>
@@ -447,13 +444,19 @@
   </si>
   <si>
     <t>pgdm25tanvi_t@mdi.ac.in</t>
+  </si>
+  <si>
+    <t>25P055</t>
+  </si>
+  <si>
+    <t>Sritam Tripathy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,6 +475,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -513,16 +522,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -842,15 +848,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B019EAA6-779E-4DEA-A874-892C07726B87}">
-  <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
@@ -861,7 +867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -872,7 +878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -884,9 +890,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A44" si="0">A3+1</f>
+        <f t="shared" ref="A4:A45" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -896,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -908,7 +914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -920,7 +926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -932,7 +938,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -944,7 +950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -956,7 +962,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -968,7 +974,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -980,7 +986,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -992,7 +998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1004,19 +1010,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1028,7 +1034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1040,7 +1046,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1052,7 +1058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1064,7 +1070,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1076,7 +1082,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1088,7 +1094,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1100,7 +1106,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1112,19 +1118,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1136,7 +1142,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1148,7 +1154,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1160,7 +1166,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1172,7 +1178,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1184,7 +1190,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1196,7 +1202,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1208,7 +1214,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1220,7 +1226,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1232,7 +1238,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1244,7 +1250,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1256,7 +1262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1268,7 +1274,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -1280,7 +1286,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -1292,7 +1298,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1304,7 +1310,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1316,7 +1322,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -1328,7 +1334,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1340,7 +1346,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1352,7 +1358,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1364,7 +1370,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -1374,6 +1380,18 @@
       </c>
       <c r="C44" s="1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1382,6 +1400,7 @@
       <sortCondition ref="B1:B44"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1390,14 +1409,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1446D57F-BA4E-43FD-A986-19C3814FF999}">
   <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="2" customWidth="1"/>
-    <col min="3" max="5" width="31.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="31.81640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
@@ -1414,7 +1433,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1427,11 +1446,11 @@
       <c r="D2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1444,11 +1463,11 @@
       <c r="D3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1461,11 +1480,11 @@
       <c r="D4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1478,11 +1497,11 @@
       <c r="D5" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1495,11 +1514,11 @@
       <c r="D6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1512,11 +1531,11 @@
       <c r="D7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1529,11 +1548,11 @@
       <c r="D8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1546,11 +1565,11 @@
       <c r="D9" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1563,11 +1582,11 @@
       <c r="D10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1580,11 +1599,11 @@
       <c r="D11" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1597,11 +1616,11 @@
       <c r="D12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1614,28 +1633,28 @@
       <c r="D13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E14" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1648,11 +1667,11 @@
       <c r="D15" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1665,11 +1684,11 @@
       <c r="D16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1682,11 +1701,11 @@
       <c r="D17" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1699,11 +1718,11 @@
       <c r="D18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1716,11 +1735,11 @@
       <c r="D19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1733,11 +1752,11 @@
       <c r="D20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1750,11 +1769,11 @@
       <c r="D21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1767,11 +1786,11 @@
       <c r="D22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1784,11 +1803,11 @@
       <c r="D23" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1801,11 +1820,11 @@
       <c r="D24" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1818,11 +1837,11 @@
       <c r="D25" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1835,11 +1854,11 @@
       <c r="D26" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1852,11 +1871,11 @@
       <c r="D27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1869,11 +1888,11 @@
       <c r="D28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1886,11 +1905,11 @@
       <c r="D29" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1903,11 +1922,11 @@
       <c r="D30" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1920,11 +1939,11 @@
       <c r="D31" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E31" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1937,11 +1956,11 @@
       <c r="D32" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E32" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1954,11 +1973,11 @@
       <c r="D33" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1971,11 +1990,11 @@
       <c r="D34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E34" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1988,11 +2007,11 @@
       <c r="D35" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2005,11 +2024,11 @@
       <c r="D36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2022,11 +2041,11 @@
       <c r="D37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2039,11 +2058,11 @@
       <c r="D38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2056,11 +2075,11 @@
       <c r="D39" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2073,11 +2092,11 @@
       <c r="D40" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2090,11 +2109,11 @@
       <c r="D41" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2107,11 +2126,11 @@
       <c r="D42" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2124,24 +2143,24 @@
       <c r="D43" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E43" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="3" t="s">
         <v>131</v>
       </c>
     </row>
